--- a/data/seed/portfolio/L-2024-1475/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-1475/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,35 +542,35 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>3730000</v>
+        <v>8058000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №251/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №2054 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45530000</v>
+        <v>49858000</v>
       </c>
     </row>
     <row r="9">
@@ -582,61 +582,61 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>3139000</v>
+        <v>8092000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №18/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №299/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48669000</v>
+        <v>57950000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>1347000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>58698000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,11 +646,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №129/26 от 02.07.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №21</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>50016000</v>
+        <v>-748000</v>
       </c>
     </row>
     <row r="11">
@@ -660,37 +660,37 @@
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>5741000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>9618000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nurafshon Yog'och MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>352083816</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000971484320001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №136/26 от 06.07.2026</t>
+          <t>Оплата за товары согласно с/ф №285</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55757000</v>
+        <v>-10366000</v>
       </c>
     </row>
     <row r="12">
@@ -700,183 +700,173 @@
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>2844000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>18570000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>329789379</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №65/26, QQS 12%</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58601000</v>
+        <v>-28936000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>2064000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>2734000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nurafshon Yog'och MChJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>352083816</t>
+          <t>276160200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000971484320001</t>
+          <t>20208000223209440001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>60665000</v>
+        <v>-31670000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>1703000</v>
+        <v>16851000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №76/26 от 06.07.2026</t>
+          <t>Оплата за продукцию по договору №195/26, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>62368000</v>
+        <v>-14819000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>7396000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>7546000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №427</t>
+          <t>SHARTNOMA №286/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>54972000</v>
+        <v>-7273000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>15250000</v>
+        <v>17100000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>322254150</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>16307000297567027417</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -886,152 +876,157 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №242/26</t>
+          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>39722000</v>
+        <v>-24373000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>18570000</v>
+        <v>45072000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Bahor Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №3696</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №69/26 ОТ 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21152000</v>
+        <v>-69445000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>92556000</v>
+        <v>26803000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Denov Plastik MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>292007960</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000937692839001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №54/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2410</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>113708000</v>
+        <v>-42642000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>4972000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>7550000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №71/26</t>
+          <t>Предоплата за товар по дог. №130/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>108736000</v>
+        <v>-35092000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>42266000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>21826000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Urganch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>392454924</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000450145581001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1041,117 +1036,117 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>151002000</v>
+        <v>-56918000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3259000</v>
+        <v>2532000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6802</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>147743000</v>
+        <v>-59450000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>1175000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>2532000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8215 за поставленный товар</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>148918000</v>
+        <v>-61982000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2734000</v>
+        <v>13302000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish Materiallari MChJ</t>
+          <t>Urganch Tekstil MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>380892454</t>
+          <t>366553492</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000247450145001</t>
+          <t>20208000250569401001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,257 +1156,262 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Оплата за транспортные услуги по договору №164/26</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>146184000</v>
+        <v>-75284000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>17100000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>34959000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
+          <t>Saodat Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>284741157</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16307000297567027417</t>
+          <t>20208000876666622001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4453 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>129084000</v>
+        <v>-40325000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>39339000</v>
+        <v>8771000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №154/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №251/26, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>168423000</v>
+        <v>-31554000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>7364000</v>
+        <v>6499000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №9/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №8573 за поставленный товар</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>175787000</v>
+        <v>-25055000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>12504000</v>
+        <v>24023000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>322254150</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8745</t>
+          <t>Оплата за упаковочные материалы, с/ф №636</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>163283000</v>
+        <v>-49078000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>32538000</v>
+        <v>56164000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mehnat Metall MChJ</t>
+          <t>Urganch Tekstil MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>346841814</t>
+          <t>366553492</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000156997881001</t>
+          <t>20208000250569401001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №108/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №109/26, QQS bilan</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>130745000</v>
+        <v>-105242000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>14756000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>1709000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olmaliq Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>355363897</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000996397142001</t>
+          <t>20208000565026670001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №177/26, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>145501000</v>
+        <v>-106951000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2532000</v>
+        <v>4695000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
@@ -1436,437 +1436,432 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>142969000</v>
+        <v>-111646000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2532000</v>
+        <v>101633000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Предоплата за материалы по договору №193/26</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>140437000</v>
+        <v>-213279000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>3971000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>212381000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Bunyodkor Moy AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>309750042</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000154603228001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №195/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №269 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>136466000</v>
+        <v>-898000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>6379000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>10776000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №77/26</t>
+          <t>SHARTNOMA №166/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>130087000</v>
+        <v>9878000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>12857000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>7004000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>322254150</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8890</t>
+          <t>Предоплата за товар по договору №273/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>117230000</v>
+        <v>16882000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>1153000</v>
+        <v>10631000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Предоплата за твар по договору №280/26 от 16.07.2026</t>
+          <t>Оплата по счет-фактуре №7938 за поставленный овар</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>118383000</v>
+        <v>27513000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3472000</v>
+        <v>8096000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Navro'z Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>225705634</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000565199521001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №29/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №203/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>114911000</v>
+        <v>19417000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46219</v>
+        <v>46233</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>9938000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>11688000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>322254150</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №255/26</t>
+          <t>Предоплата за товар по договору №209/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>104973000</v>
+        <v>31105000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46233</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>2219000</v>
+        <v>8062000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6561 17.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №156/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>107192000</v>
+        <v>39167000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>83668000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>7256000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №251/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №275/26</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>190860000</v>
+        <v>31911000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>15378000</v>
+        <v>5589000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Tong Logistik MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>334255238</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000531902576001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2198 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №182/26, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>206238000</v>
+        <v>37500000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>3526000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>368214422</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,677 +1871,667 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3245 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>209764000</v>
+        <v>37200000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>3976000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>190882000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №953</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3839 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>205788000</v>
+        <v>228082000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>5122000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>43976000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>356024159</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000225106117001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №43/26 от 20.07.2026, НДС 12%</t>
+          <t>Оплата по с/ф №8804 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>200666000</v>
+        <v>272058000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>13333000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>5478000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №114/26</t>
+          <t>Предоплата за товар по договору №244/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>187333000</v>
+        <v>277536000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>170862000</v>
+        <v>18602000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>398097500</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000271546032001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №290/26</t>
+          <t>Tovarlar uchun to'lov h/f №4422</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16471000</v>
+        <v>258934000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46224</v>
+        <v>46238</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>22602000</v>
+        <v>5571000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №283/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №283/26 от 04.08.2026</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>39073000</v>
+        <v>264505000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1709000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>5443000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Olmaliq Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>250228292</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000810996381001</t>
+          <t>20208000103159015001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по договору №67/26, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>37364000</v>
+        <v>269948000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46226</v>
+        <v>46239</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>4558000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>26457000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Trans Servis XK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>227499094</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000135601939001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №5883 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32806000</v>
+        <v>296405000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>4272000</v>
+        <v>6591000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №298/26 от 24.07.2026</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8987 ОТ 05.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>37078000</v>
+        <v>302996000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>4862000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>7140000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
+          <t>Urganch Tekstil MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>329789379</t>
+          <t>366553492</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>20208000250569401001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2730 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплта за материалы по договору №60/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>41940000</v>
+        <v>295856000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>4232000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>12190000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Navro'z Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>225705634</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565199521001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6273 27.07.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №8606</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46172000</v>
+        <v>283666000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>2821000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>18811000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>313627317</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9176 ОТ 27.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>48993000</v>
+        <v>264855000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46230</v>
+        <v>46241</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>1274000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>7301000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>370274990</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000491356019001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5560 27.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №122/26</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>50267000</v>
+        <v>257554000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46230</v>
+        <v>46241</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3203000</v>
+        <v>12536000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3128</t>
+          <t>Оплата за транспортные услуги по дог. №281/26</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>47064000</v>
+        <v>245018000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>3822000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>15593000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8192</t>
+          <t>Оплата по счет-фактуре №1437 за поставленный товар</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>43242000</v>
+        <v>260611000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>7625000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>6282000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Bunyodkor Moy AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>309750042</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000154603228001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №54/26 от 27.07.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2630 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35617000</v>
+        <v>266893000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>3030000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>2769000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>276160200</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000223209440001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9330 за поставленный товар</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38647000</v>
+        <v>264124000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>1946000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>368214422</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>16307000297567027417</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2556,747 +2541,757 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>40593000</v>
+        <v>247024000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>1159000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>28379000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SHARTNOMA №192/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за материалы по договору №69/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>41752000</v>
+        <v>218645000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>3592000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>26707000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4410</t>
+          <t>Предоплата за товар по договору №12/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>38160000</v>
+        <v>245352000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>5921000</v>
+        <v>4131000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9702 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №21/26, НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>44081000</v>
+        <v>249483000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>1205000</v>
+        <v>3218000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №223/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №1733 за поставленный товар</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45286000</v>
+        <v>252701000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46234</v>
+        <v>46247</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2523000</v>
+        <v>2113000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>329789379</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5073 ОТ 31.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7697 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>47809000</v>
+        <v>254814000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>5180000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Qarshi Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>356024159</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000225106117001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5133 14.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>47509000</v>
+        <v>259994000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46251</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>3070000</v>
+        <v>2565000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №218/26</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>44439000</v>
+        <v>257429000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46234</v>
+        <v>46251</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>3392000</v>
+        <v>2565000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №148/26</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>41047000</v>
+        <v>254864000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>19382000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>77361000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4265 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №294/26</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>60429000</v>
+        <v>177503000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>12772000</v>
+        <v>8565000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>329789379</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №216/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №153/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>73201000</v>
+        <v>186068000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>9888000</v>
+        <v>10787000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6190 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №1162 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>83089000</v>
+        <v>196855000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>4909000</v>
+        <v>8134000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Shartnoma №284/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №252/26 от 19.08.2026</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>87998000</v>
+        <v>204989000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>4901000</v>
+        <v>6464000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>370274990</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000491356019001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6913 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №104/26, QQS 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>92899000</v>
+        <v>211453000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>1830000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>17918000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9909 03.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №199/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>94729000</v>
+        <v>193535000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46237</v>
+        <v>46255</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>20936000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>3793000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3387</t>
+          <t>Оплата по счет-фактуре №5691 за поставленный товар</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>73793000</v>
+        <v>197328000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46239</v>
+        <v>46255</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>3973000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>4814000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №177/26 от 05.08.2026</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>77766000</v>
+        <v>192514000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>2101000</v>
+        <v>4998000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8925 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>79867000</v>
+        <v>197512000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>18811000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>2066000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Denov Agro Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>268793414</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000854551833001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>61056000</v>
+        <v>199578000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>3048000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>1731000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565026670001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,117 +3301,117 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №53/26 от 06.08.2026</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>64104000</v>
+        <v>197847000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>2578000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>16701000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2292 06.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №288/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>66682000</v>
+        <v>181146000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46240</v>
+        <v>46259</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>5008000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>8748000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>284741157</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000876666622001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №115/26</t>
+          <t>Оплата за товар по счет-фактуре №1142 от 25.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>61674000</v>
+        <v>189894000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46240</v>
+        <v>46259</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>18525000</v>
+        <v>10757000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3426,37 +3421,37 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
+          <t>Предоплата за материалы по договору №129/26</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>43149000</v>
+        <v>179137000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46241</v>
+        <v>46259</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>3506000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>27870000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Urganch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>392454924</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000450145581001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3466,37 +3461,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5616 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №208/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46655000</v>
+        <v>151267000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>2558000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>368214422</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3506,37 +3496,37 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №235/26 от 07.08.2026</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>49213000</v>
+        <v>150967000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>2769000</v>
+        <v>14046000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish Materiallari MChJ</t>
+          <t>Andijon Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>380892454</t>
+          <t>317261697</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000247450145001</t>
+          <t>20208000278591812001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3546,77 +3536,77 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №86/21</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №263/26</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46444000</v>
+        <v>136921000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46241</v>
+        <v>46265</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>6909000</v>
+        <v>15326000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №24/26</t>
+          <t>Оплата за транспортные услуги по договору №231/26</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>39535000</v>
+        <v>121595000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>3381000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>16568000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Urganch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>392454924</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000450145581001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3626,112 +3616,117 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №193/26 от 10.08.2026</t>
+          <t>Предоплата за материалы по договору №168/26</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>42916000</v>
+        <v>105027000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>2281000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>25171000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Olmaliq Mato MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>382887433</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000923617758001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2547 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №3996</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>45197000</v>
+        <v>79856000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>1736000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>45261000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Navro'z Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>225705634</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565199521001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6886 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №9020</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46933000</v>
+        <v>34595000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46244</v>
+        <v>46266</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>17100000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>19951000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
+          <t>Bunyodkor Moy AJ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>309750042</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16307000297567027417</t>
+          <t>20208000154603228001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3741,277 +3736,272 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по дог. №158/26, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>29833000</v>
+        <v>54546000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46245</v>
+        <v>46266</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>1895000</v>
+        <v>4154000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №269/26, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>31728000</v>
+        <v>58700000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46246</v>
+        <v>46266</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>55914000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>20645000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4787 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №39/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>87642000</v>
+        <v>38055000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46247</v>
+        <v>46267</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>3888000</v>
+        <v>5161000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3060 13.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>91530000</v>
+        <v>43216000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46247</v>
+        <v>46268</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>3637000</v>
+        <v>27866000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1597</t>
+          <t>Оплата за товар по счет-фактуре №4129 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>95167000</v>
+        <v>71082000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46247</v>
+        <v>46268</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>19224000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>4090000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Tong Logistik MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>334255238</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000531902576001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3536</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №42/26 ОТ 03.09.2026</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>75943000</v>
+        <v>75172000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46248</v>
+        <v>46268</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>8887000</v>
+        <v>3430000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2080 14.08.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №150/26 ОТ 03.09.2026</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>84830000</v>
+        <v>78602000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46248</v>
+        <v>46269</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>2113000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>20327000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>368214422</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4021,1037 +4011,1032 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1411 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №1993</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>86943000</v>
+        <v>58275000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>4683000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>13330000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за упаковоные материалы, с/ф №9178</t>
+          <t>Оплата по с/ф №1308 за поставленный товар</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>82260000</v>
+        <v>71605000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>10295000</v>
+        <v>5874000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №48/26 от 17.08.2026</t>
+          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>92555000</v>
+        <v>77479000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>9181000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>11616000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №188/26, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>101736000</v>
+        <v>65863000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46251</v>
+        <v>46273</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>1653000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>2992000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Namangan Dori-Darmon AJ</t>
+          <t>Ishonch Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>231687934</t>
+          <t>276160200</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000448545518001</t>
+          <t>20208000223209440001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №80/26 от 17.08.2026</t>
+          <t>Аренда помещения за сентябрь, дог. №12/25</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>103389000</v>
+        <v>62871000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46251</v>
+        <v>46273</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>1570000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>10528000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Navro'z Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>225705634</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565199521001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №29/26, QQS bilan</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>104959000</v>
+        <v>52343000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>2565000</v>
+        <v>17100000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000297567027417</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>102394000</v>
+        <v>35243000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>2565000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>8975000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>284741157</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000876666622001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Оплата по счет-фактуре №5608 за поставленный товар</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>99829000</v>
+        <v>44218000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>3260000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>7637000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>322254150</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №44/26, QQS bilan</t>
+          <t>Оплаа за товар по счет-фактуре №9059 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>96569000</v>
+        <v>51855000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>5379000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>4878000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №203/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>91190000</v>
+        <v>56733000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46252</v>
+        <v>46279</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>10767000</v>
+        <v>3881000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9176 от 18.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5794 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>101957000</v>
+        <v>60614000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46252</v>
+        <v>46279</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>6561000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2772000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9912 18.08.2026, QQS bilan</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>108518000</v>
+        <v>57842000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46252</v>
+        <v>46279</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>33989000</v>
+        <v>2772000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №242/26</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>74529000</v>
+        <v>55070000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46253</v>
+        <v>46279</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>29141000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>7627000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Olmaliq Mato MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>382887433</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000923617758001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9606 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №32/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>103670000</v>
+        <v>47443000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46254</v>
+        <v>46279</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>4527000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>12581000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1965 20.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №24/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>108197000</v>
+        <v>34862000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46254</v>
+        <v>46279</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>2018000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>24712000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Agro MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>384181411</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000699788155001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №225/26 от 20.08.2026</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8111</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>110215000</v>
+        <v>10150000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46255</v>
+        <v>46282</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>2058000</v>
+        <v>7623000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №151/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №97/26 от 17.09.2026</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>112273000</v>
+        <v>17773000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46255</v>
+        <v>46282</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>4626000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>4787000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Shartnoma №59/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>107647000</v>
+        <v>22560000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46255</v>
+        <v>46283</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>59438000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>29159000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qo'qon Sut MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>258563469</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000045897494001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9365</t>
+          <t>Оплата за товар по счет-фактуре №9317 от 18.09.2026, в т.ч. НДС12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>48209000</v>
+        <v>51719000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46258</v>
+        <v>46283</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>27368000</v>
+        <v>19751000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3763 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №257/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>75577000</v>
+        <v>71470000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46258</v>
+        <v>46283</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>17823000</v>
+        <v>5233000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7130 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №214/26, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>93400000</v>
+        <v>76703000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>10382000</v>
+        <v>10819000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №105/26 от 24.08.2026</t>
+          <t>Оплата за продукцию по договору №153/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>103782000</v>
+        <v>87522000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>5959000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>6409000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №238/26</t>
+          <t>Оплата за товар по с/ф №1433 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>97823000</v>
+        <v>93931000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>18246000</v>
+        <v>5128000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3970</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>79577000</v>
+        <v>88803000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>47116000</v>
+        <v>11287000</v>
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Qo'qon Metall Servis XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>381615650</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000919249774001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1916</t>
+          <t>Оплата за транспортные услуги по договору №285/26</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>32461000</v>
+        <v>77516000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46261</v>
+        <v>46286</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>1731000</v>
+        <v>36926000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000810996381001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №2728</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>30730000</v>
+        <v>40590000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46261</v>
+        <v>46286</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>3331000</v>
+        <v>70701000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sarbon Trans Servis MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>398097500</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000271546032001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5061,117 +5046,117 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №221/26</t>
+          <t>Предоплата за материалы по договору №193/26</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>27399000</v>
+        <v>-30111000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46262</v>
+        <v>46287</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>5119000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>34937000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №133/26</t>
+          <t>Оплата по счет-фактуре №3956 за поставленный товар</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>22280000</v>
+        <v>4826000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46262</v>
+        <v>46287</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>45095000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>11604000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kamalak Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>209828874</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000319236177001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8254</t>
+          <t>Оплата за товар по счет-фактуре №1957 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-22815000</v>
+        <v>16430000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>37428000</v>
+        <v>8890000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bunyodkor Moy AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>309750042</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000154603228001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5181,197 +5166,197 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №394</t>
+          <t>Оплата за продукцию по договору №86/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>14613000</v>
+        <v>25320000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>35307000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>62640000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №678 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №5381</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>49920000</v>
+        <v>-37320000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46265</v>
+        <v>46288</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>6219000</v>
+        <v>9459000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>284741157</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000876666622001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №7/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №138/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>56139000</v>
+        <v>-27861000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>5573000</v>
+        <v>9131000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>262731761</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000061409017001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9876 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>61712000</v>
+        <v>-18730000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>4425000</v>
+        <v>7460000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Saodat Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>284741157</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000876666622001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5095</t>
+          <t>Оплата за товар по счет-фактуре №3475 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>66137000</v>
+        <v>-11270000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46265</v>
+        <v>46289</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>2982000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>1870000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565026670001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5381,552 +5366,557 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №272/26 ОТ 31.08.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>69119000</v>
+        <v>-13140000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46265</v>
+        <v>46290</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>2562000</v>
+        <v>6529000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №677 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №277/26, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>71681000</v>
+        <v>-6611000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46265</v>
+        <v>46290</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>2505000</v>
+        <v>4100000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>329789379</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9678</t>
+          <t>Оплата за товар по с/ф №9817 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>74186000</v>
+        <v>-2511000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46265</v>
+        <v>46293</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>107154000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Oqtosh Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Оплата за продукцию по дог. №205/26, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>73886000</v>
+        <v>104643000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46265</v>
+        <v>46293</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>9611000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>7525000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>322254150</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000407366532001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1205</t>
+          <t>Оплата за товар по счет-фактуре №4019 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>64275000</v>
+        <v>112168000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46265</v>
+        <v>46293</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>25817000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>3578000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Ilhom Meva Eksport XK</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>227089288</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000190266418001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №158/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7259</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>38458000</v>
+        <v>115746000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46267</v>
+        <v>46293</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>3242000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>6485000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Navro'z Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>225705634</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000565199521001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Shartnoma №115/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №194/26 ОТ 28.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>41700000</v>
+        <v>109261000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46267</v>
+        <v>46293</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>2702000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>8312000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №224/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7348</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>44402000</v>
+        <v>100949000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46267</v>
+        <v>46293</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>1029000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>10797000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Olmaliq Mato MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>382887433</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000923617758001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №245/26 ОТ 02.09.2026</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №170/26</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>45431000</v>
+        <v>90152000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46267</v>
+        <v>46293</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>997000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>43890000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Olmaliq Mato MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>382887433</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000923617758001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №88/26 ОТ 02.09.2026</t>
+          <t>Оплата за транспортные услуги по договору №196/26</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46428000</v>
+        <v>46262000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>602000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>11350000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №116/26 от 02.09.2026</t>
+          <t>Оплата за транспортные услуги по дог. №221/26</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>47030000</v>
+        <v>34912000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>920000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>12337000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Termiz Mehmonxona MChJ</t>
+          <t>Bahor Qurilish MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>368214422</t>
+          <t>356346990</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000510222264001</t>
+          <t>20208000589749441001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №250/26 от 29.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>47950000</v>
+        <v>22575000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>2078000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>14198000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nukus Sut XK</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>393502282</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000201031590001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №190/26 т 03.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №32/26, НДС 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>45872000</v>
+        <v>36773000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46269</v>
+        <v>46295</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>6198000</v>
+        <v>6375000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Urganch Yog'och MChJ</t>
+          <t>Oqtosh Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>394847411</t>
+          <t>321442275</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000718766666001</t>
+          <t>20208000022226448001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №206/26, НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>52070000</v>
+        <v>43148000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>6222000</v>
+        <v>3409000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Angren Metall Servis MChJ</t>
+          <t>Tong Logistik MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>313627317</t>
+          <t>334255238</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000110614090001</t>
+          <t>20208000531902576001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5936,2341 +5926,111 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №214/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6224 от 30.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>58292000</v>
+        <v>46557000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>2723000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ziyo Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>329789379</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000926300902001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №272/26 от 07.09.2026</t>
+          <t>Комиссия за еревод</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>61015000</v>
+        <v>46257000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>2315000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>10957000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gulshan Oziq-ovqat Savdo MChJ</t>
+          <t>Urganch Tekstil MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>219342552</t>
+          <t>366553492</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000855319025001</t>
+          <t>20208000250569401001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7311 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3598</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>63330000</v>
+        <v>35300000</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>777000</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Namangan Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>231687934</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000448545518001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №286/26 от 07.09.2026</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>64107000</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>1226294000</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>1219794000</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>612000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №89/26 от 07.09.2026</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>64719000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>2248000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №179/26</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>62471000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>2844000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>322254150</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000407366532001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №6910</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>59627000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B150" t="n">
-        <v>242</v>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>20327000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №3849</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>39300000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B151" t="n">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>166120000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Kamalak Sut XK</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>209828874</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000319236177001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №220/26</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>-126820000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B152" t="n">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>1529000</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №220/26 от 08.09.2026</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>-125291000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B153" t="n">
-        <v>245</v>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>9160000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Sarbon Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>398097500</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000271546032001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно с/ф №3957</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>-134451000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B154" t="n">
-        <v>246</v>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>9866000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №775</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>-144317000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B155" t="n">
-        <v>247</v>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>1649000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №5494</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>-145966000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>2992000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Lazzat Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>380892454</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000247450145001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №86/21</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>-148958000</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>23075000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Kamalak Sut XK</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>209828874</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000319236177001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №4567</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>-172033000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>1324000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №2325 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>-170709000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>3778000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №2530</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>-174487000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>17100000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1475)</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>16307000297567027417</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2024-1475 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>-191587000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>1844000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №234/26 от 11.09.2026</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>-189743000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>731000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №215/26 от 11.09.2026</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>-189012000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>6301000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №187/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>-182711000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>616000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №8663 от 14.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>-182095000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>3620000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №123/26 от 14.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>-185715000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>5710000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №37/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>-180005000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B167" t="n">
-        <v>259</v>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>11454000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №183/26 от 16.09.2026</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>-168551000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>663000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №197/26 от 16.09.2026</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>-167888000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>571000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Shartnoma №83/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>-167317000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>2772000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Уплата социального налога за август</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>-170089000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>2772000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>НДФЛ за август 2026</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>-172861000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>6592000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Buxoro Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>322254150</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000407366532001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №159/26 от 16.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>-179453000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>21905000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №295/26</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>-201358000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>1297000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №220/26 ОТ 17.09.2026</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>-200061000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>911000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №2662 от 17.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>-199150000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>522000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №65/26 от 17.09.2026</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>-198628000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>4003000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №41/26 от 17.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>-202631000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n">
-        <v>804000</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1085 18.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>-201827000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>2614000</v>
-      </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Kamalak Sut XK</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>209828874</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000319236177001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №3187</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>-204441000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>53863000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №92/26</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>-258304000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n"/>
-      <c r="D181" s="2" t="n">
-        <v>1945000</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №63/26 ОТ 21.09.2026</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>-256359000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>1717000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №203/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>-254642000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>1234000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Angren Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>370274990</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000491356019001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4600</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>-253408000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>1217000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2870</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>-252191000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>818000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №980 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>-251373000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>638000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №62/26 от 21.09.2026</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>-250735000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B187" t="n">
-        <v>279</v>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>630000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Ziyo Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>329789379</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000926300902001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Shartnoma №157/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n">
-        <v>-250105000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B188" t="n">
-        <v>280</v>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>598000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №6755 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>-249507000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B189" t="n">
-        <v>281</v>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>4037000</v>
-      </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Kamalak Sut XK</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>209828874</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000319236177001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №4756</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>-253544000</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B190" t="n">
-        <v>282</v>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>4883000</v>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>НДС за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>-258427000</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B191" t="n">
-        <v>283</v>
-      </c>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n">
-        <v>2105000</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Angren Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>313627317</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>20208000110614090001</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>SHARTNOMA №131/26 BO'YICHA OLDINDAN TO'LOV</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="n">
-        <v>-256322000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B192" t="n">
-        <v>284</v>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>1797000</v>
-      </c>
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Qo'qon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>258563469</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>20208000045897494001</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №6256</t>
-        </is>
-      </c>
-      <c r="J192" s="2" t="n">
-        <v>-258119000</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B193" t="n">
-        <v>285</v>
-      </c>
-      <c r="C193" s="2" t="n">
-        <v>1870000</v>
-      </c>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>20208000810996381001</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>ELEKTR ENERGIYASI UCHUN TO'LOV SENTYABR</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="n">
-        <v>-259989000</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B194" t="n">
-        <v>286</v>
-      </c>
-      <c r="C194" s="2" t="n">
-        <v>2385000</v>
-      </c>
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №204/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="n">
-        <v>-262374000</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B195" t="n">
-        <v>287</v>
-      </c>
-      <c r="C195" s="2" t="n">
-        <v>35386000</v>
-      </c>
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Nukus Sut XK</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>393502282</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>20208000201031590001</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №170/26</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="n">
-        <v>-297760000</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B196" t="n">
-        <v>288</v>
-      </c>
-      <c r="C196" s="2" t="n"/>
-      <c r="D196" s="2" t="n">
-        <v>323355000</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2287 29.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="n">
-        <v>25595000</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B197" t="n">
-        <v>289</v>
-      </c>
-      <c r="C197" s="2" t="n"/>
-      <c r="D197" s="2" t="n">
-        <v>4110000</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №3054 от 29.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J197" s="2" t="n">
-        <v>29705000</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B198" t="n">
-        <v>290</v>
-      </c>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n">
-        <v>3347000</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №107/26 от 29.09.2026</t>
-        </is>
-      </c>
-      <c r="J198" s="2" t="n">
-        <v>33052000</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B199" t="n">
-        <v>291</v>
-      </c>
-      <c r="C199" s="2" t="n"/>
-      <c r="D199" s="2" t="n">
-        <v>1297000</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>Shartnoma №28/6 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="n">
-        <v>34349000</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B200" t="n">
-        <v>292</v>
-      </c>
-      <c r="C200" s="2" t="n"/>
-      <c r="D200" s="2" t="n">
-        <v>1251000</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Termiz Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>368214422</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>20208000510222264001</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J200" s="2" t="n">
-        <v>35600000</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B201" t="n">
-        <v>293</v>
-      </c>
-      <c r="C201" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>Комиссия за перевод</t>
-        </is>
-      </c>
-      <c r="J201" s="2" t="n">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
         <v>35300000</v>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="n">
-        <v>1178716000</v>
-      </c>
-      <c r="D202" s="4" t="n">
-        <v>1172216000</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>35300000</v>
-      </c>
-      <c r="D203" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
